--- a/Zinc/6. Statistical data analysis/Typology_Developed_lulc Interaction/interaction_results.xlsx
+++ b/Zinc/6. Statistical data analysis/Typology_Developed_lulc Interaction/interaction_results.xlsx
@@ -428,10 +428,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>7.77576782399158</v>
+        <v>7.73729118794566</v>
       </c>
       <c r="D2" t="n">
-        <v>4.58452081118545e-236</v>
+        <v>5.34199153822107e-221</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -445,10 +445,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00237879501905521</v>
+        <v>0.00252042596433481</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0788461215880143</v>
+        <v>0.0867540976577475</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -462,10 +462,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0114728046059699</v>
+        <v>-0.0116144355512495</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00168418138429827</v>
+        <v>0.00232002760349231</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.00758434103539486</v>
+        <v>-0.00767923483844597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000220635335827755</v>
+        <v>0.0000750301393871371</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -496,10 +496,10 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0000914913692591961</v>
+        <v>-0.00194370232661126</v>
       </c>
       <c r="D6" t="n">
-        <v>0.962548875591803</v>
+        <v>0.325764291348542</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -513,10 +513,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.3431996466088</v>
+        <v>5.37478472331756</v>
       </c>
       <c r="D7" t="n">
-        <v>5.62467480080732e-235</v>
+        <v>8.91364278495987e-226</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -530,10 +530,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.00066379614207068</v>
+        <v>-0.000767524924503085</v>
       </c>
       <c r="D8" t="n">
-        <v>0.477939766014083</v>
+        <v>0.436783079690062</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -547,10 +547,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00478534970602743</v>
+        <v>0.00488907848845984</v>
       </c>
       <c r="D9" t="n">
-        <v>0.057334987168938</v>
+        <v>0.0553469065164775</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -564,10 +564,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00384991442055517</v>
+        <v>0.00321362135158014</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00175239598122941</v>
+        <v>0.0130105414577085</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00377791761866144</v>
+        <v>0.00269472747076626</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00535599604672066</v>
+        <v>0.0430472885115167</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -598,7 +598,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>6.37002550619458</v>
+        <v>6.37604663193184</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -615,10 +615,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00119465438137877</v>
+        <v>0.00112372176873422</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0118723230293206</v>
+        <v>0.020267640692389</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -632,10 +632,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00851808208453698</v>
+        <v>-0.00844714947189244</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0000000000764714010720324</v>
+        <v>0.0000000000467592935483805</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -649,10 +649,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.00147110377543684</v>
+        <v>-0.00180861138866633</v>
       </c>
       <c r="D15" t="n">
-        <v>0.017662845328411</v>
+        <v>0.00429676565311138</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -666,10 +666,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000979531950086912</v>
+        <v>0.000978121124122622</v>
       </c>
       <c r="D16" t="n">
-        <v>0.151495472021642</v>
+        <v>0.132450100498173</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -683,10 +683,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>5.51852342957118</v>
+        <v>5.56171654626366</v>
       </c>
       <c r="D17" t="n">
-        <v>1.41753874156885e-254</v>
+        <v>1.16598997537204e-243</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -700,10 +700,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0026617609127704</v>
+        <v>0.00185460523527661</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00173260207389179</v>
+        <v>0.040329278088556</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
@@ -717,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0117489791757571</v>
+        <v>0.0125561348532509</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000000359325669301171</v>
+        <v>0.000000122558423424282</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -734,10 +734,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00260978736914048</v>
+        <v>0.00324893329862827</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0183625831252345</v>
+        <v>0.00606771992107563</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -751,10 +751,10 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>0.000574141881769947</v>
+        <v>0.00104781071790504</v>
       </c>
       <c r="D21" t="n">
-        <v>0.637207411422238</v>
+        <v>0.388274873033932</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -768,7 +768,7 @@
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>6.02725975687968</v>
+        <v>6.03746979986744</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00176028504044888</v>
+        <v>0.00155346233350238</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000481076729996506</v>
+        <v>0.00290705798868371</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -802,10 +802,10 @@
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0048699906109797</v>
+        <v>-0.00466316790403321</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000324733311262547</v>
+        <v>0.000545834138317522</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -819,10 +819,10 @@
         <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.00259079470262439</v>
+        <v>-0.00276351058158139</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0000871516605243717</v>
+        <v>0.000054717533331657</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -836,10 +836,10 @@
         <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00132166679063568</v>
+        <v>0.00119606073316985</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0674763366534105</v>
+        <v>0.0871964013793033</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -853,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>5.72014375344473</v>
+        <v>5.70900759044497</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.000437108756602712</v>
+        <v>-0.000343004736264217</v>
       </c>
       <c r="D28" t="n">
-        <v>0.332308188757878</v>
+        <v>0.470069729317889</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.00672215351619742</v>
+        <v>-0.00681625753653593</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0000000538844832678086</v>
+        <v>0.0000000507086811369743</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -904,10 +904,10 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00041215454728111</v>
+        <v>0.000138557329015553</v>
       </c>
       <c r="D30" t="n">
-        <v>0.483967920058512</v>
+        <v>0.823114940964456</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -921,13 +921,13 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00141323913746221</v>
+        <v>0.00113378133231211</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0302538280126723</v>
+        <v>0.0766337923994294</v>
       </c>
       <c r="E31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -938,10 +938,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>5.3333877282453</v>
+        <v>5.33651903229522</v>
       </c>
       <c r="D32" t="n">
-        <v>3.65423733318021e-240</v>
+        <v>1.90308857262309e-220</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -955,10 +955,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>0.000139947015646627</v>
+        <v>-0.000123041009316416</v>
       </c>
       <c r="D33" t="n">
-        <v>0.876492646829842</v>
+        <v>0.903678725807949</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0174524624574646</v>
+        <v>0.0177154504824276</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0000000000032353601482062</v>
+        <v>0.0000000000584003903167318</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -989,10 +989,10 @@
         <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.00299545430622485</v>
+        <v>-0.00323438141681116</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0112584149451632</v>
+        <v>0.0152715291164738</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00404484315025424</v>
+        <v>0.00175272860454725</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00198662757009613</v>
+        <v>0.200824327398499</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1023,10 +1023,10 @@
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>5.64645950341029</v>
+        <v>5.71704181755627</v>
       </c>
       <c r="D37" t="n">
-        <v>4.14808630782694e-280</v>
+        <v>2.75086992251286e-268</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1040,13 +1040,13 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>0.00144175776269865</v>
+        <v>0.000249532917697583</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0474511278232027</v>
+        <v>0.749973533634411</v>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1057,10 +1057,10 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0100062708837559</v>
+        <v>0.0111984957287569</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000000456208112773616</v>
+        <v>0.0000000570735505064514</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1074,10 +1074,10 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00103181694169728</v>
+        <v>0.00198958666607322</v>
       </c>
       <c r="D40" t="n">
-        <v>0.276585540499912</v>
+        <v>0.0522946931899641</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1091,10 +1091,10 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00232582351551634</v>
+        <v>0.00268153621472575</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0267655007616912</v>
+        <v>0.0113214794460252</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
@@ -1108,10 +1108,10 @@
         <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>4.9748979211723</v>
+        <v>5.04781907745552</v>
       </c>
       <c r="D42" t="n">
-        <v>2.1104142863546e-291</v>
+        <v>7.22316936917691e-289</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -1125,10 +1125,10 @@
         <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.00218731258625844</v>
+        <v>-0.00318805402862154</v>
       </c>
       <c r="D43" t="n">
-        <v>0.000252634078665739</v>
+        <v>0.000000198742351055823</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1142,10 +1142,10 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0069222334555088</v>
+        <v>0.00792297489787191</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0000173153044017697</v>
+        <v>0.000000523844321942731</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1159,10 +1159,10 @@
         <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00184613163623467</v>
+        <v>0.00262128150421247</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0174303178995184</v>
+        <v>0.000923011986400165</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1176,10 +1176,10 @@
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00355278339741776</v>
+        <v>0.0039052736651207</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0000396192380081143</v>
+        <v>0.00000205164518892221</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1193,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>2.041809121012</v>
+        <v>2.11793749240565</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000798715562444592</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000252440360511927</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1210,10 +1210,10 @@
         <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>0.00077616869835118</v>
+        <v>-0.000190888850721609</v>
       </c>
       <c r="D48" t="n">
-        <v>0.442686611762726</v>
+        <v>0.853834656178799</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1227,10 +1227,10 @@
         <v>8</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00245907575832646</v>
+        <v>0.00342613330739923</v>
       </c>
       <c r="D49" t="n">
-        <v>0.365180042499469</v>
+        <v>0.200396998067375</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1244,13 +1244,13 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00248919582209299</v>
+        <v>0.00296126250029965</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0600462047854684</v>
+        <v>0.0291681591755392</v>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1261,10 +1261,10 @@
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.000381451934011418</v>
+        <v>0.0010205936224673</v>
       </c>
       <c r="D51" t="n">
-        <v>0.793629471858713</v>
+        <v>0.464475491278076</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1278,10 +1278,10 @@
         <v>6</v>
       </c>
       <c r="C52" t="n">
-        <v>1.10536917190083</v>
+        <v>1.37654511312659</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00000000000000000384396045953912</v>
+        <v>0.000000000000000000000000253082620053081</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
@@ -1295,13 +1295,13 @@
         <v>7</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00566582065570934</v>
+        <v>0.00216072248576331</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00169589375491957</v>
+        <v>0.227689105378282</v>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1312,10 +1312,10 @@
         <v>8</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.00383227022171355</v>
+        <v>-0.000327172051767517</v>
       </c>
       <c r="D54" t="n">
-        <v>0.42610103950414</v>
+        <v>0.943486850959276</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0000661155737361669</v>
+        <v>0.00290360280758011</v>
       </c>
       <c r="D55" t="n">
-        <v>0.977473495460375</v>
+        <v>0.214469556631699</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1346,10 +1346,10 @@
         <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00586539121923472</v>
+        <v>0.00816897408420881</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0238180496210345</v>
+        <v>0.000767546971533587</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>

--- a/Zinc/6. Statistical data analysis/Typology_Developed_lulc Interaction/interaction_results.xlsx
+++ b/Zinc/6. Statistical data analysis/Typology_Developed_lulc Interaction/interaction_results.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">Developed_lulc</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed_lulc:TypologyNP Tribs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Developed_lulc:TypologyP Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">Developed_lulc:TypologyPD Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed_lulc:TypologyMain Stem</t>
   </si>
   <si>
     <t xml:space="preserve">log_DOC_nM</t>
@@ -428,10 +428,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>7.73729118794566</v>
+        <v>7.59039495085791</v>
       </c>
       <c r="D2" t="n">
-        <v>5.34199153822107e-221</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000114232384283568</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -445,13 +445,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00252042596433481</v>
+        <v>-0.00909400958691471</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0867540976577475</v>
+        <v>0.00954140088456565</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -462,13 +462,13 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0116144355512495</v>
+        <v>0.00393520071280355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00232002760349231</v>
+        <v>0.288288685934523</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.00767923483844597</v>
+        <v>0.00967073322463824</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000750301393871371</v>
+        <v>0.00994659956974226</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -496,13 +496,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.00194370232661126</v>
+        <v>0.0116144355512495</v>
       </c>
       <c r="D6" t="n">
-        <v>0.325764291348542</v>
+        <v>0.00232002760349224</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -513,10 +513,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.37478472331756</v>
+        <v>4.88209000323968</v>
       </c>
       <c r="D7" t="n">
-        <v>8.91364278495987e-226</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000396814455772886</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -530,10 +530,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.000767524924503085</v>
+        <v>0.00412155356395681</v>
       </c>
       <c r="D8" t="n">
-        <v>0.436783079690062</v>
+        <v>0.0795787732614982</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -547,10 +547,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00488907848845984</v>
+        <v>-0.00167545713687975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0553469065164775</v>
+        <v>0.500780647152879</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -564,13 +564,13 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00321362135158014</v>
+        <v>-0.00219435101769362</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0130105414577085</v>
+        <v>0.381970878586943</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00269472747076626</v>
+        <v>-0.00488907848845991</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0430472885115167</v>
+        <v>0.0553469065164736</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -598,10 +598,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>6.37604663193184</v>
+        <v>5.83281427298288</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4.63463683889942e-262</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -615,10 +615,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00112372176873422</v>
+        <v>-0.00732342770315823</v>
       </c>
       <c r="D13" t="n">
-        <v>0.020267640692389</v>
+        <v>0.00000000052640150674927</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -632,10 +632,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00844714947189244</v>
+        <v>0.00663853808322612</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0000000000467592935483805</v>
+        <v>0.0000000890870275423979</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -649,10 +649,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.00180861138866633</v>
+        <v>0.00942527059601506</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00429676565311138</v>
+        <v>0.000000000000149619929678416</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -666,13 +666,13 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000978121124122622</v>
+        <v>0.00844714947189244</v>
       </c>
       <c r="D16" t="n">
-        <v>0.132450100498173</v>
+        <v>0.0000000000467592935483749</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -683,10 +683,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>5.56171654626366</v>
+        <v>4.15053528244781</v>
       </c>
       <c r="D17" t="n">
-        <v>1.16598997537204e-243</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000433392678099137</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -700,10 +700,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00185460523527661</v>
+        <v>0.0144107400885275</v>
       </c>
       <c r="D18" t="n">
-        <v>0.040329278088556</v>
+        <v>0.0000000000719155145662361</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
@@ -717,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0125561348532509</v>
+        <v>-0.0093072015546226</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000000122558423424282</v>
+        <v>0.0000523599562909365</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -734,10 +734,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00324893329862827</v>
+        <v>-0.0115083241353458</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00606771992107563</v>
+        <v>0.000000816434608839048</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -751,13 +751,13 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00104781071790504</v>
+        <v>-0.0125561348532509</v>
       </c>
       <c r="D21" t="n">
-        <v>0.388274873033932</v>
+        <v>0.000000122558423424286</v>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -768,10 +768,10 @@
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>6.03746979986744</v>
+        <v>5.25563299887961</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2.21118301580674e-236</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -785,10 +785,10 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00155346233350238</v>
+        <v>-0.00310970557053079</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00290705798868371</v>
+        <v>0.0120285666583999</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -802,13 +802,13 @@
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.00466316790403321</v>
+        <v>0.00189965732245178</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000545834138317522</v>
+        <v>0.146798277196298</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -819,10 +819,10 @@
         <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.00276351058158139</v>
+        <v>0.00585922863720303</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000054717533331657</v>
+        <v>0.0000116755119610679</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -836,13 +836,13 @@
         <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00119606073316985</v>
+        <v>0.00466316790403316</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0871964013793033</v>
+        <v>0.000545834138317571</v>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -853,10 +853,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>5.70900759044497</v>
+        <v>5.20309706686212</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1.05721049356194e-247</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.000343004736264217</v>
+        <v>-0.00715926227280011</v>
       </c>
       <c r="D28" t="n">
-        <v>0.470069729317889</v>
+        <v>0.000000000680281274316577</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -887,10 +887,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.00681625753653593</v>
+        <v>0.00695481486555144</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0000000507086811369743</v>
+        <v>0.0000000137468796368392</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -904,13 +904,13 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>0.000138557329015553</v>
+        <v>0.00795003886884799</v>
       </c>
       <c r="D30" t="n">
-        <v>0.823114940964456</v>
+        <v>0.000000000161216164673418</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +921,13 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00113378133231211</v>
+        <v>0.00681625753653587</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0766337923994294</v>
+        <v>0.0000000507086811369826</v>
       </c>
       <c r="E31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -938,10 +938,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>5.33651903229522</v>
+        <v>3.58386111587137</v>
       </c>
       <c r="D32" t="n">
-        <v>1.90308857262309e-220</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000458834901534211</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -955,13 +955,13 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.000123041009316416</v>
+        <v>0.0175924094731112</v>
       </c>
       <c r="D33" t="n">
-        <v>0.903678725807949</v>
+        <v>0.00000000000220656390652635</v>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +972,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0177154504824276</v>
+        <v>-0.0209498318992387</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0000000000584003903167318</v>
+        <v>0.00000000000000548918708321081</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -989,10 +989,10 @@
         <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.00323438141681116</v>
+        <v>-0.0159627218778803</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0152715291164738</v>
+        <v>0.00000000180281374296449</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00175272860454725</v>
+        <v>-0.0177154504824276</v>
       </c>
       <c r="D36" t="n">
-        <v>0.200824327398499</v>
+        <v>0.0000000000584003903167312</v>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1023,10 +1023,10 @@
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>5.71704181755627</v>
+        <v>4.28702342546733</v>
       </c>
       <c r="D37" t="n">
-        <v>2.75086992251286e-268</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000423279676802418</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1040,13 +1040,13 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>0.000249532917697583</v>
+        <v>0.0114480286464545</v>
       </c>
       <c r="D38" t="n">
-        <v>0.749973533634411</v>
+        <v>0.00000000208280195912178</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1057,10 +1057,10 @@
         <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0111984957287569</v>
+        <v>-0.00920890906268368</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0000000570735505064514</v>
+        <v>0.00000435657461286225</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1074,13 +1074,13 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00198958666607322</v>
+        <v>-0.00851695951403113</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0522946931899641</v>
+        <v>0.0000240816415181524</v>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1091,10 +1091,10 @@
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00268153621472575</v>
+        <v>-0.0111984957287569</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0113214794460252</v>
+        <v>0.0000000570735505064557</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
@@ -1108,10 +1108,10 @@
         <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>5.04781907745552</v>
+        <v>4.10843158404021</v>
       </c>
       <c r="D42" t="n">
-        <v>7.22316936917691e-289</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000931332135729894</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -1125,10 +1125,10 @@
         <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.00318805402862154</v>
+        <v>0.00473492086925034</v>
       </c>
       <c r="D43" t="n">
-        <v>0.000000198742351055823</v>
+        <v>0.00101275952269813</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1142,10 +1142,10 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00792297489787191</v>
+        <v>-0.00530169339365941</v>
       </c>
       <c r="D44" t="n">
-        <v>0.000000523844321942731</v>
+        <v>0.000525727950149347</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1159,10 +1159,10 @@
         <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00262128150421247</v>
+        <v>-0.00401770123275117</v>
       </c>
       <c r="D45" t="n">
-        <v>0.000923011986400165</v>
+        <v>0.00890799736599573</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1176,10 +1176,10 @@
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0039052736651207</v>
+        <v>-0.00792297489787188</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00000205164518892221</v>
+        <v>0.000000523844321942749</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1193,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>2.11793749240565</v>
+        <v>1.82626146981727</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000252440360511927</v>
+        <v>0.00000000000000000000000000000000000000250150697871412</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1210,10 +1210,10 @@
         <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.000190888850721609</v>
+        <v>0.00323524445667765</v>
       </c>
       <c r="D48" t="n">
-        <v>0.853834656178799</v>
+        <v>0.189659658009892</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1227,10 +1227,10 @@
         <v>8</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00342613330739923</v>
+        <v>-0.000464870807099603</v>
       </c>
       <c r="D49" t="n">
-        <v>0.200396998067375</v>
+        <v>0.858785110349024</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1244,13 +1244,13 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00296126250029965</v>
+        <v>-0.00240553968493195</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0291681591755392</v>
+        <v>0.361494214545617</v>
       </c>
       <c r="E50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1261,10 +1261,10 @@
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0010205936224673</v>
+        <v>-0.00342613330739926</v>
       </c>
       <c r="D51" t="n">
-        <v>0.464475491278076</v>
+        <v>0.20039699806737</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1278,13 +1278,13 @@
         <v>6</v>
       </c>
       <c r="C52" t="n">
-        <v>1.37654511312659</v>
+        <v>0.254838067310161</v>
       </c>
       <c r="D52" t="n">
-        <v>0.000000000000000000000000253082620053081</v>
+        <v>0.228258573325261</v>
       </c>
       <c r="E52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1295,10 +1295,10 @@
         <v>7</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00216072248576331</v>
+        <v>0.00183355043399588</v>
       </c>
       <c r="D53" t="n">
-        <v>0.227689105378282</v>
+        <v>0.666524298092797</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         <v>8</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.000327172051767517</v>
+        <v>0.00323077485934754</v>
       </c>
       <c r="D54" t="n">
-        <v>0.943486850959276</v>
+        <v>0.474117966899602</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00290360280758011</v>
+        <v>0.00849614613597627</v>
       </c>
       <c r="D55" t="n">
-        <v>0.214469556631699</v>
+        <v>0.0624909117093802</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1346,13 +1346,13 @@
         <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00816897408420881</v>
+        <v>0.000327172051767406</v>
       </c>
       <c r="D56" t="n">
-        <v>0.000767546971533587</v>
+        <v>0.943486850959296</v>
       </c>
       <c r="E56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/6. Statistical data analysis/Typology_Developed_lulc Interaction/interaction_results.xlsx
+++ b/Zinc/6. Statistical data analysis/Typology_Developed_lulc Interaction/interaction_results.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">Developed_lulc</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed_lulc:TypologyNon-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed_lulc:TypologyPerennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed_lulc:TypologyDeveloped Tribs</t>
+    <t xml:space="preserve">Developed_lulc:TypologyNon-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed_lulc:TypologyPerennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed_lulc:TypologyDeveloped Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">Developed_lulc:TypologyMain Stem</t>
